--- a/Courses/Term 3/QAM-III/Case Studies/801 - DATA - S&P500 INDEX.xlsx
+++ b/Courses/Term 3/QAM-III/Case Studies/801 - DATA - S&P500 INDEX.xlsx
@@ -5,16 +5,85 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MBA\Courses\Term 3\QAM-III\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MBA\Courses\Term 3\QAM-III\Case Studies\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEFD9437-E486-42A2-A8C8-83A9564308CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D49B5EB0-D97B-4BCF-A3ED-D0C508D044A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{B2BED8D6-8C7E-0E42-9D17-93C443EBC8CA}"/>
   </bookViews>
   <sheets>
     <sheet name="Making an NDEX Fund p345" sheetId="3" r:id="rId1"/>
+    <sheet name="SOLUTION" sheetId="4" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="solver_adj" localSheetId="0" hidden="1">'Making an NDEX Fund p345'!$H$13:$H$18</definedName>
+    <definedName name="solver_adj" localSheetId="1" hidden="1">SOLUTION!$B$22:$B$27</definedName>
+    <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="1" hidden="1">0.0001</definedName>
+    <definedName name="solver_drv" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="1" hidden="1">2147483647</definedName>
+    <definedName name="solver_lhs1" localSheetId="0" hidden="1">'Making an NDEX Fund p345'!$H$20</definedName>
+    <definedName name="solver_lhs1" localSheetId="1" hidden="1">SOLUTION!$B$22:$B$27</definedName>
+    <definedName name="solver_lhs2" localSheetId="0" hidden="1">'Making an NDEX Fund p345'!$H$20</definedName>
+    <definedName name="solver_lhs2" localSheetId="1" hidden="1">SOLUTION!$K$7</definedName>
+    <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="1" hidden="1">2147483647</definedName>
+    <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="1" hidden="1">30</definedName>
+    <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="1" hidden="1">0.075</definedName>
+    <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="1" hidden="1">2</definedName>
+    <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="1" hidden="1">2147483647</definedName>
+    <definedName name="solver_num" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_num" localSheetId="1" hidden="1">2</definedName>
+    <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_opt" localSheetId="0" hidden="1">'Making an NDEX Fund p345'!$G$24</definedName>
+    <definedName name="solver_opt" localSheetId="1" hidden="1">SOLUTION!$Q$7</definedName>
+    <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="1" hidden="1">0.000001</definedName>
+    <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rel1" localSheetId="1" hidden="1">3</definedName>
+    <definedName name="solver_rel2" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rel2" localSheetId="1" hidden="1">3</definedName>
+    <definedName name="solver_rhs1" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rhs1" localSheetId="1" hidden="1">0</definedName>
+    <definedName name="solver_rhs2" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rhs2" localSheetId="1" hidden="1">SOLUTION!$L$7</definedName>
+    <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="1" hidden="1">2</definedName>
+    <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="1" hidden="1">0</definedName>
+    <definedName name="solver_scl" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_sho" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="1" hidden="1">2</definedName>
+    <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="1" hidden="1">100</definedName>
+    <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="1" hidden="1">2147483647</definedName>
+    <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="1" hidden="1">0.01</definedName>
+    <definedName name="solver_typ" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_typ" localSheetId="1" hidden="1">2</definedName>
+    <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="1" hidden="1">0</definedName>
+    <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="1" hidden="1">3</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -35,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="53">
   <si>
     <t xml:space="preserve">Index Funds by finance companies are very popular across the mutual fund industry. It is a passive asset mgmt process where you make a portfolio with stocks, mutual funds and other securities in such a way that it competes with and even beats the established market index like S&amp;P500 etc. Vanguard in the US has over $ 200 b in AUM, </t>
   </si>
@@ -119,15 +188,100 @@
   </si>
   <si>
     <t xml:space="preserve">Several fund managers aspire to beat the market (given by S&amp;P 500 index) and hence show their "acumen" in designing great portfolio for the common investor. </t>
+  </si>
+  <si>
+    <t>Fund</t>
+  </si>
+  <si>
+    <t>Large-Cap Growth</t>
+  </si>
+  <si>
+    <t>Large-Cap Value</t>
+  </si>
+  <si>
+    <t>Small-Cap Growth</t>
+  </si>
+  <si>
+    <t>Small-Cap Value</t>
+  </si>
+  <si>
+    <t>Fund / Year</t>
+  </si>
+  <si>
+    <t>Y1</t>
+  </si>
+  <si>
+    <t>Y2</t>
+  </si>
+  <si>
+    <t>Y3</t>
+  </si>
+  <si>
+    <t>Y4</t>
+  </si>
+  <si>
+    <t>Y5</t>
+  </si>
+  <si>
+    <t>Int-Term Bond</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>PORTFOLIO</t>
+  </si>
+  <si>
+    <t>DIFFERENCE</t>
+  </si>
+  <si>
+    <t>SQ.DIFFERENCE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL DEVIATION </t>
+  </si>
+  <si>
+    <t>AVERAGE</t>
+  </si>
+  <si>
+    <t>FOR YEAR 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXPECTED RETURN </t>
+  </si>
+  <si>
+    <t>DEVIATION</t>
+  </si>
+  <si>
+    <t>SQ DEVIATION</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>INVESTMENT/ DECISION VARIABLE AS %</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="169" formatCode="0.00000000000000000"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -148,7 +302,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -167,6 +321,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -177,24 +349,65 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="12" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="12" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="1" fillId="4" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="40% - Accent2" xfId="1" builtinId="35"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -507,11 +720,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C43CC6F-7E8F-7643-8DD9-676D7BF3B446}">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.296875" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
+    <col min="8" max="8" width="34.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="69" customHeight="1" x14ac:dyDescent="0.3">
@@ -657,133 +871,147 @@
       <c r="F12" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="H12" s="1"/>
+      <c r="H12" s="21" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="20">
         <v>10.06</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="20">
         <v>13.12</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="20">
         <v>13.47</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="20">
         <v>45.42</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="20">
         <v>-21.93</v>
       </c>
-      <c r="H13" s="1"/>
+      <c r="H13" s="22">
+        <v>0.30333785573398253</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="20">
         <v>17.64</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="20">
         <v>3.25</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="20">
         <v>7.51</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="20">
         <v>-1.33</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="20">
         <v>7.36</v>
       </c>
-      <c r="H14" s="1"/>
+      <c r="H14" s="23">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>15</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="20">
         <v>32.409999999999997</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="20">
         <v>18.71</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="20">
         <v>33.28</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="20">
         <v>41.46</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="20">
         <v>-23.26</v>
       </c>
-      <c r="H15" s="1"/>
+      <c r="H15" s="23">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>16</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="20">
         <v>32.36</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="20">
         <v>20.61</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="20">
         <v>12.93</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="20">
         <v>7.06</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="20">
         <v>-5.37</v>
       </c>
-      <c r="H16" s="1"/>
+      <c r="H16" s="23">
+        <v>0.36498152011098395</v>
+      </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>17</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="20">
         <v>33.44</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="20">
         <v>19.399999999999999</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="20">
         <v>3.85</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="20">
         <v>58.68</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="20">
         <v>-9.02</v>
       </c>
-      <c r="H17" s="1"/>
+      <c r="H17" s="23">
+        <v>0.22655144544540542</v>
+      </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="20">
         <v>24.56</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="20">
         <v>25.32</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="20">
         <v>-6.7</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="20">
         <v>5.43</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="20">
         <v>17.309999999999999</v>
       </c>
-      <c r="H18" s="1"/>
+      <c r="H18" s="23">
+        <v>0.10512918209684266</v>
+      </c>
     </row>
     <row r="20" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
@@ -804,19 +1032,115 @@
       <c r="F20" s="5">
         <v>-10</v>
       </c>
+      <c r="H20" s="24">
+        <f>SUM(H13:H18)</f>
+        <v>1.0000000033872145</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G21" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>48</v>
+      </c>
+      <c r="B22" s="25">
+        <f>SUMPRODUCT(B$13:B$18,$H$13:$H$18)</f>
+        <v>25.020233867468114</v>
+      </c>
+      <c r="C22" s="25">
+        <f t="shared" ref="C22:F22" si="0">SUMPRODUCT(C$13:C$18,$H$13:$H$18)</f>
+        <v>18.55903072905015</v>
+      </c>
+      <c r="D22" s="25">
+        <f t="shared" si="0"/>
+        <v>8.9730295166877312</v>
+      </c>
+      <c r="E22" s="25">
+        <f t="shared" si="0"/>
+        <v>30.219265216943281</v>
+      </c>
+      <c r="F22" s="25">
+        <f t="shared" si="0"/>
+        <v>-8.8358578350634307</v>
+      </c>
+      <c r="G22" s="25">
+        <f>SUM(B22:F22)</f>
+        <v>73.935701495085837</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>49</v>
+      </c>
+      <c r="B23" s="20">
+        <f>B22-B20</f>
+        <v>2.0233867468114397E-2</v>
+      </c>
+      <c r="C23" s="20">
+        <f t="shared" ref="C23:F23" si="1">C22-C20</f>
+        <v>-1.4409692709498501</v>
+      </c>
+      <c r="D23" s="20">
+        <f t="shared" si="1"/>
+        <v>0.97302951668773119</v>
+      </c>
+      <c r="E23" s="20">
+        <f t="shared" si="1"/>
+        <v>0.21926521694328116</v>
+      </c>
+      <c r="F23" s="20">
+        <f t="shared" si="1"/>
+        <v>1.1641421649365693</v>
+      </c>
+      <c r="G23" s="20">
+        <f t="shared" ref="G23:G24" si="2">SUM(B23:F23)</f>
+        <v>0.93570149508584599</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" s="20">
+        <f>B23*B23</f>
+        <v>4.0940939271721813E-4</v>
+      </c>
+      <c r="C24" s="20">
+        <f t="shared" ref="C24:F24" si="3">C23*C23</f>
+        <v>2.0763924398217424</v>
+      </c>
+      <c r="D24" s="20">
+        <f t="shared" si="3"/>
+        <v>0.9467864403455597</v>
+      </c>
+      <c r="E24" s="20">
+        <f t="shared" si="3"/>
+        <v>4.8077235361184155E-2</v>
+      </c>
+      <c r="F24" s="20">
+        <f t="shared" si="3"/>
+        <v>1.3552269801832024</v>
+      </c>
+      <c r="G24" s="26">
+        <f t="shared" si="2"/>
+        <v>4.4268925051044059</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>26</v>
       </c>
     </row>
@@ -825,7 +1149,408 @@
     <mergeCell ref="A1:H2"/>
     <mergeCell ref="A9:H10"/>
   </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4775E015-58BC-43CD-9976-59314F657FA1}">
+  <dimension ref="A1:Q28"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="16.09765625" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="5.3984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.796875" style="9"/>
+    <col min="9" max="9" width="10.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.796875" style="9"/>
+    <col min="11" max="11" width="12.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.69921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.8984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.59765625" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.796875" style="9"/>
+    <col min="16" max="16" width="16.3984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.59765625" style="9" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="8.796875" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B1" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="J1" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B2" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="12">
+        <v>10.06</v>
+      </c>
+      <c r="D2" s="12">
+        <v>13.12</v>
+      </c>
+      <c r="E2" s="12">
+        <v>13.47</v>
+      </c>
+      <c r="F2" s="12">
+        <v>45.42</v>
+      </c>
+      <c r="G2" s="12">
+        <v>-21.93</v>
+      </c>
+      <c r="J2" s="9">
+        <v>1</v>
+      </c>
+      <c r="K2" s="9">
+        <f>SUMPRODUCT(C$2:C$7,$B$22:$B$27)</f>
+        <v>24.899562728466826</v>
+      </c>
+      <c r="L2" s="11">
+        <v>25</v>
+      </c>
+      <c r="M2" s="15">
+        <f>K2-L2</f>
+        <v>-0.10043727153317406</v>
+      </c>
+      <c r="N2" s="16">
+        <f>M2*M2</f>
+        <v>1.0087645513028536E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="12">
+        <v>17.64</v>
+      </c>
+      <c r="D3" s="12">
+        <v>3.25</v>
+      </c>
+      <c r="E3" s="12">
+        <v>7.51</v>
+      </c>
+      <c r="F3" s="12">
+        <v>-1.33</v>
+      </c>
+      <c r="G3" s="12">
+        <v>7.36</v>
+      </c>
+      <c r="J3" s="9">
+        <v>2</v>
+      </c>
+      <c r="K3" s="9">
+        <f>SUMPRODUCT(D$2:D$7,$B$22:$B$27)</f>
+        <v>16.627281725565577</v>
+      </c>
+      <c r="L3" s="11">
+        <v>20</v>
+      </c>
+      <c r="M3" s="15">
+        <f t="shared" ref="M3:M6" si="0">K3-L3</f>
+        <v>-3.3727182744344226</v>
+      </c>
+      <c r="N3" s="16">
+        <f t="shared" ref="N3:N6" si="1">M3*M3</f>
+        <v>11.37522855870391</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B4" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="12">
+        <v>32.409999999999997</v>
+      </c>
+      <c r="D4" s="12">
+        <v>18.71</v>
+      </c>
+      <c r="E4" s="12">
+        <v>33.28</v>
+      </c>
+      <c r="F4" s="12">
+        <v>41.46</v>
+      </c>
+      <c r="G4" s="12">
+        <v>-23.26</v>
+      </c>
+      <c r="J4" s="9">
+        <v>3</v>
+      </c>
+      <c r="K4" s="9">
+        <f>SUMPRODUCT(E$2:E$7,$B$22:$B$27)</f>
+        <v>10.706198228945436</v>
+      </c>
+      <c r="L4" s="11">
+        <v>8</v>
+      </c>
+      <c r="M4" s="15">
+        <f t="shared" si="0"/>
+        <v>2.7061982289454356</v>
+      </c>
+      <c r="N4" s="16">
+        <f t="shared" si="1"/>
+        <v>7.3235088543474127</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B5" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="12">
+        <v>32.36</v>
+      </c>
+      <c r="D5" s="12">
+        <v>20.61</v>
+      </c>
+      <c r="E5" s="12">
+        <v>12.93</v>
+      </c>
+      <c r="F5" s="12">
+        <v>7.06</v>
+      </c>
+      <c r="G5" s="12">
+        <v>-5.37</v>
+      </c>
+      <c r="J5" s="9">
+        <v>4</v>
+      </c>
+      <c r="K5" s="9">
+        <f>SUMPRODUCT(F$2:F$7,$B$22:$B$27)</f>
+        <v>25.819923950389526</v>
+      </c>
+      <c r="L5" s="11">
+        <v>30</v>
+      </c>
+      <c r="M5" s="15">
+        <f t="shared" si="0"/>
+        <v>-4.1800760496104736</v>
+      </c>
+      <c r="N5" s="16">
+        <f t="shared" si="1"/>
+        <v>17.473035780527102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B6" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="12">
+        <v>33.44</v>
+      </c>
+      <c r="D6" s="12">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="E6" s="12">
+        <v>3.85</v>
+      </c>
+      <c r="F6" s="12">
+        <v>58.68</v>
+      </c>
+      <c r="G6" s="12">
+        <v>-9.02</v>
+      </c>
+      <c r="J6" s="9">
+        <v>5</v>
+      </c>
+      <c r="K6" s="9">
+        <f>SUMPRODUCT(G$2:G$7,$B$22:$B$27)</f>
+        <v>-5.7787717532690035</v>
+      </c>
+      <c r="L6" s="11">
+        <v>-10</v>
+      </c>
+      <c r="M6" s="15">
+        <f t="shared" si="0"/>
+        <v>4.2212282467309965</v>
+      </c>
+      <c r="N6" s="16">
+        <f t="shared" si="1"/>
+        <v>17.818767910999643</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B7" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="12">
+        <v>24.56</v>
+      </c>
+      <c r="D7" s="12">
+        <v>25.32</v>
+      </c>
+      <c r="E7" s="12">
+        <v>-6.7</v>
+      </c>
+      <c r="F7" s="12">
+        <v>5.43</v>
+      </c>
+      <c r="G7" s="12">
+        <v>17.309999999999999</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="K7" s="9">
+        <f>AVERAGE(K2:K6)</f>
+        <v>14.454838976019673</v>
+      </c>
+      <c r="L7" s="9">
+        <f>AVERAGE(L2:L6)</f>
+        <v>14.6</v>
+      </c>
+      <c r="P7" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q7" s="16">
+        <f>SUM(N2:N6)</f>
+        <v>54.000628750091096</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="15">
+        <f>AVERAGE(C2:C7)</f>
+        <v>25.078333333333333</v>
+      </c>
+      <c r="D8" s="15">
+        <f t="shared" ref="D8:G8" si="2">AVERAGE(D2:D7)</f>
+        <v>16.734999999999999</v>
+      </c>
+      <c r="E8" s="15">
+        <f t="shared" si="2"/>
+        <v>10.723333333333331</v>
+      </c>
+      <c r="F8" s="15">
+        <f t="shared" si="2"/>
+        <v>26.120000000000005</v>
+      </c>
+      <c r="G8" s="15">
+        <f t="shared" si="2"/>
+        <v>-5.8183333333333325</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B12" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="19">
+        <v>25</v>
+      </c>
+      <c r="D12" s="19">
+        <v>20</v>
+      </c>
+      <c r="E12" s="19">
+        <v>8</v>
+      </c>
+      <c r="F12" s="19">
+        <v>30</v>
+      </c>
+      <c r="G12" s="19">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="I13" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="13">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="13">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="13">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" s="13">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" s="13">
+        <v>0.16158637509351526</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="13">
+        <v>0.16630487291013885</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B28" s="17">
+        <f>SUM(B22:B27)</f>
+        <v>0.99455791467032073</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Courses/Term 3/QAM-III/Case Studies/801 - DATA - S&P500 INDEX.xlsx
+++ b/Courses/Term 3/QAM-III/Case Studies/801 - DATA - S&P500 INDEX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MBA\Courses\Term 3\QAM-III\Case Studies\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D49B5EB0-D97B-4BCF-A3ED-D0C508D044A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B9F5547-157B-4E81-AAE4-43A636636749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{B2BED8D6-8C7E-0E42-9D17-93C443EBC8CA}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="54">
   <si>
     <t xml:space="preserve">Index Funds by finance companies are very popular across the mutual fund industry. It is a passive asset mgmt process where you make a portfolio with stocks, mutual funds and other securities in such a way that it competes with and even beats the established market index like S&amp;P500 etc. Vanguard in the US has over $ 200 b in AUM, </t>
   </si>
@@ -263,6 +263,9 @@
   </si>
   <si>
     <t>INVESTMENT/ DECISION VARIABLE AS %</t>
+  </si>
+  <si>
+    <t>SSE</t>
   </si>
 </sst>
 </file>
@@ -270,7 +273,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="0.00000000000000000"/>
+    <numFmt numFmtId="164" formatCode="0.00000000000000000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -353,7 +356,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -363,13 +366,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -382,17 +381,15 @@
     <xf numFmtId="12" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="12" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="12" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -405,6 +402,9 @@
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="1" fillId="4" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="40% - Accent2" xfId="1" builtinId="35"/>
@@ -729,26 +729,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="69" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:8" ht="3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
+      <c r="A2" s="23"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -821,26 +821,26 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="23"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
+      <c r="A10" s="23"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="23"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
@@ -871,7 +871,7 @@
       <c r="F12" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="H12" s="21" t="s">
+      <c r="H12" s="17" t="s">
         <v>52</v>
       </c>
     </row>
@@ -879,22 +879,22 @@
       <c r="A13" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="20">
+      <c r="B13" s="12">
         <v>10.06</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="12">
         <v>13.12</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="12">
         <v>13.47</v>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="12">
         <v>45.42</v>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="12">
         <v>-21.93</v>
       </c>
-      <c r="H13" s="22">
+      <c r="H13" s="18">
         <v>0.30333785573398253</v>
       </c>
     </row>
@@ -902,22 +902,22 @@
       <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="20">
+      <c r="B14" s="12">
         <v>17.64</v>
       </c>
-      <c r="C14" s="20">
+      <c r="C14" s="12">
         <v>3.25</v>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="12">
         <v>7.51</v>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="12">
         <v>-1.33</v>
       </c>
-      <c r="F14" s="20">
+      <c r="F14" s="12">
         <v>7.36</v>
       </c>
-      <c r="H14" s="23">
+      <c r="H14" s="19">
         <v>0</v>
       </c>
     </row>
@@ -925,22 +925,22 @@
       <c r="A15" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="20">
+      <c r="B15" s="12">
         <v>32.409999999999997</v>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="12">
         <v>18.71</v>
       </c>
-      <c r="D15" s="20">
+      <c r="D15" s="12">
         <v>33.28</v>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="12">
         <v>41.46</v>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="12">
         <v>-23.26</v>
       </c>
-      <c r="H15" s="23">
+      <c r="H15" s="19">
         <v>0</v>
       </c>
     </row>
@@ -948,22 +948,22 @@
       <c r="A16" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="20">
+      <c r="B16" s="12">
         <v>32.36</v>
       </c>
-      <c r="C16" s="20">
+      <c r="C16" s="12">
         <v>20.61</v>
       </c>
-      <c r="D16" s="20">
+      <c r="D16" s="12">
         <v>12.93</v>
       </c>
-      <c r="E16" s="20">
+      <c r="E16" s="12">
         <v>7.06</v>
       </c>
-      <c r="F16" s="20">
+      <c r="F16" s="12">
         <v>-5.37</v>
       </c>
-      <c r="H16" s="23">
+      <c r="H16" s="19">
         <v>0.36498152011098395</v>
       </c>
     </row>
@@ -971,22 +971,22 @@
       <c r="A17" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="20">
+      <c r="B17" s="12">
         <v>33.44</v>
       </c>
-      <c r="C17" s="20">
+      <c r="C17" s="12">
         <v>19.399999999999999</v>
       </c>
-      <c r="D17" s="20">
+      <c r="D17" s="12">
         <v>3.85</v>
       </c>
-      <c r="E17" s="20">
+      <c r="E17" s="12">
         <v>58.68</v>
       </c>
-      <c r="F17" s="20">
+      <c r="F17" s="12">
         <v>-9.02</v>
       </c>
-      <c r="H17" s="23">
+      <c r="H17" s="19">
         <v>0.22655144544540542</v>
       </c>
     </row>
@@ -994,22 +994,22 @@
       <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="20">
+      <c r="B18" s="12">
         <v>24.56</v>
       </c>
-      <c r="C18" s="20">
+      <c r="C18" s="12">
         <v>25.32</v>
       </c>
-      <c r="D18" s="20">
+      <c r="D18" s="12">
         <v>-6.7</v>
       </c>
-      <c r="E18" s="20">
+      <c r="E18" s="12">
         <v>5.43</v>
       </c>
-      <c r="F18" s="20">
+      <c r="F18" s="12">
         <v>17.309999999999999</v>
       </c>
-      <c r="H18" s="23">
+      <c r="H18" s="19">
         <v>0.10512918209684266</v>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
       <c r="F20" s="5">
         <v>-10</v>
       </c>
-      <c r="H20" s="24">
+      <c r="H20" s="20">
         <f>SUM(H13:H18)</f>
         <v>1.0000000033872145</v>
       </c>
@@ -1046,27 +1046,27 @@
       <c r="A22" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="25">
+      <c r="B22" s="21">
         <f>SUMPRODUCT(B$13:B$18,$H$13:$H$18)</f>
         <v>25.020233867468114</v>
       </c>
-      <c r="C22" s="25">
+      <c r="C22" s="21">
         <f t="shared" ref="C22:F22" si="0">SUMPRODUCT(C$13:C$18,$H$13:$H$18)</f>
         <v>18.55903072905015</v>
       </c>
-      <c r="D22" s="25">
+      <c r="D22" s="21">
         <f t="shared" si="0"/>
         <v>8.9730295166877312</v>
       </c>
-      <c r="E22" s="25">
+      <c r="E22" s="21">
         <f t="shared" si="0"/>
         <v>30.219265216943281</v>
       </c>
-      <c r="F22" s="25">
+      <c r="F22" s="21">
         <f t="shared" si="0"/>
         <v>-8.8358578350634307</v>
       </c>
-      <c r="G22" s="25">
+      <c r="G22" s="21">
         <f>SUM(B22:F22)</f>
         <v>73.935701495085837</v>
       </c>
@@ -1075,27 +1075,27 @@
       <c r="A23" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="20">
+      <c r="B23" s="12">
         <f>B22-B20</f>
         <v>2.0233867468114397E-2</v>
       </c>
-      <c r="C23" s="20">
+      <c r="C23" s="12">
         <f t="shared" ref="C23:F23" si="1">C22-C20</f>
         <v>-1.4409692709498501</v>
       </c>
-      <c r="D23" s="20">
+      <c r="D23" s="12">
         <f t="shared" si="1"/>
         <v>0.97302951668773119</v>
       </c>
-      <c r="E23" s="20">
+      <c r="E23" s="12">
         <f t="shared" si="1"/>
         <v>0.21926521694328116</v>
       </c>
-      <c r="F23" s="20">
+      <c r="F23" s="12">
         <f t="shared" si="1"/>
         <v>1.1641421649365693</v>
       </c>
-      <c r="G23" s="20">
+      <c r="G23" s="12">
         <f t="shared" ref="G23:G24" si="2">SUM(B23:F23)</f>
         <v>0.93570149508584599</v>
       </c>
@@ -1104,29 +1104,32 @@
       <c r="A24" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="20">
+      <c r="B24" s="12">
         <f>B23*B23</f>
         <v>4.0940939271721813E-4</v>
       </c>
-      <c r="C24" s="20">
+      <c r="C24" s="12">
         <f t="shared" ref="C24:F24" si="3">C23*C23</f>
         <v>2.0763924398217424</v>
       </c>
-      <c r="D24" s="20">
+      <c r="D24" s="12">
         <f t="shared" si="3"/>
         <v>0.9467864403455597</v>
       </c>
-      <c r="E24" s="20">
+      <c r="E24" s="12">
         <f t="shared" si="3"/>
         <v>4.8077235361184155E-2</v>
       </c>
-      <c r="F24" s="20">
+      <c r="F24" s="12">
         <f t="shared" si="3"/>
         <v>1.3552269801832024</v>
       </c>
-      <c r="G24" s="26">
+      <c r="G24" s="22">
         <f t="shared" si="2"/>
         <v>4.4268925051044059</v>
+      </c>
+      <c r="H24" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
@@ -1159,393 +1162,389 @@
   <dimension ref="A1:Q28"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="16.09765625" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="5.3984375" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.796875" style="9"/>
-    <col min="9" max="9" width="10.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.796875" style="9"/>
-    <col min="11" max="11" width="12.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.69921875" style="9" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.8984375" style="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.59765625" style="9" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.796875" style="9"/>
-    <col min="16" max="16" width="16.3984375" style="9" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="20.59765625" style="9" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="8.796875" style="9"/>
+    <col min="1" max="2" width="16.09765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="5.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.69921875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.8984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.59765625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.3984375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" t="s">
         <v>42</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" t="s">
         <v>43</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="10">
         <v>10.06</v>
       </c>
-      <c r="D2" s="12">
+      <c r="D2" s="10">
         <v>13.12</v>
       </c>
-      <c r="E2" s="12">
+      <c r="E2" s="10">
         <v>13.47</v>
       </c>
-      <c r="F2" s="12">
+      <c r="F2" s="10">
         <v>45.42</v>
       </c>
-      <c r="G2" s="12">
+      <c r="G2" s="10">
         <v>-21.93</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2">
         <v>1</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2">
         <f>SUMPRODUCT(C$2:C$7,$B$22:$B$27)</f>
         <v>24.899562728466826</v>
       </c>
-      <c r="L2" s="11">
+      <c r="L2" s="9">
         <v>25</v>
       </c>
-      <c r="M2" s="15">
+      <c r="M2" s="12">
         <f>K2-L2</f>
         <v>-0.10043727153317406</v>
       </c>
-      <c r="N2" s="16">
+      <c r="N2" s="13">
         <f>M2*M2</f>
         <v>1.0087645513028536E-2</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="10">
         <v>17.64</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="10">
         <v>3.25</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="10">
         <v>7.51</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="10">
         <v>-1.33</v>
       </c>
-      <c r="G3" s="12">
+      <c r="G3" s="10">
         <v>7.36</v>
       </c>
-      <c r="J3" s="9">
+      <c r="J3">
         <v>2</v>
       </c>
-      <c r="K3" s="9">
+      <c r="K3">
         <f>SUMPRODUCT(D$2:D$7,$B$22:$B$27)</f>
         <v>16.627281725565577</v>
       </c>
-      <c r="L3" s="11">
+      <c r="L3" s="9">
         <v>20</v>
       </c>
-      <c r="M3" s="15">
+      <c r="M3" s="12">
         <f t="shared" ref="M3:M6" si="0">K3-L3</f>
         <v>-3.3727182744344226</v>
       </c>
-      <c r="N3" s="16">
+      <c r="N3" s="13">
         <f t="shared" ref="N3:N6" si="1">M3*M3</f>
         <v>11.37522855870391</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="10">
         <v>32.409999999999997</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="10">
         <v>18.71</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="10">
         <v>33.28</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="10">
         <v>41.46</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="10">
         <v>-23.26</v>
       </c>
-      <c r="J4" s="9">
+      <c r="J4">
         <v>3</v>
       </c>
-      <c r="K4" s="9">
+      <c r="K4">
         <f>SUMPRODUCT(E$2:E$7,$B$22:$B$27)</f>
         <v>10.706198228945436</v>
       </c>
-      <c r="L4" s="11">
+      <c r="L4" s="9">
         <v>8</v>
       </c>
-      <c r="M4" s="15">
+      <c r="M4" s="12">
         <f t="shared" si="0"/>
         <v>2.7061982289454356</v>
       </c>
-      <c r="N4" s="16">
+      <c r="N4" s="13">
         <f t="shared" si="1"/>
         <v>7.3235088543474127</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="10">
         <v>32.36</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="10">
         <v>20.61</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="10">
         <v>12.93</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="10">
         <v>7.06</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="10">
         <v>-5.37</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5">
         <v>4</v>
       </c>
-      <c r="K5" s="9">
+      <c r="K5">
         <f>SUMPRODUCT(F$2:F$7,$B$22:$B$27)</f>
         <v>25.819923950389526</v>
       </c>
-      <c r="L5" s="11">
+      <c r="L5" s="9">
         <v>30</v>
       </c>
-      <c r="M5" s="15">
+      <c r="M5" s="12">
         <f t="shared" si="0"/>
         <v>-4.1800760496104736</v>
       </c>
-      <c r="N5" s="16">
+      <c r="N5" s="13">
         <f t="shared" si="1"/>
         <v>17.473035780527102</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="10">
         <v>33.44</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="10">
         <v>19.399999999999999</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="10">
         <v>3.85</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="10">
         <v>58.68</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="10">
         <v>-9.02</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6">
         <v>5</v>
       </c>
-      <c r="K6" s="9">
+      <c r="K6">
         <f>SUMPRODUCT(G$2:G$7,$B$22:$B$27)</f>
         <v>-5.7787717532690035</v>
       </c>
-      <c r="L6" s="11">
+      <c r="L6" s="9">
         <v>-10</v>
       </c>
-      <c r="M6" s="15">
+      <c r="M6" s="12">
         <f t="shared" si="0"/>
         <v>4.2212282467309965</v>
       </c>
-      <c r="N6" s="16">
+      <c r="N6" s="13">
         <f t="shared" si="1"/>
         <v>17.818767910999643</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="10">
         <v>24.56</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="10">
         <v>25.32</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="10">
         <v>-6.7</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="10">
         <v>5.43</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="10">
         <v>17.309999999999999</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="J7" t="s">
         <v>46</v>
       </c>
-      <c r="K7" s="9">
+      <c r="K7">
         <f>AVERAGE(K2:K6)</f>
         <v>14.454838976019673</v>
       </c>
-      <c r="L7" s="9">
+      <c r="L7">
         <f>AVERAGE(L2:L6)</f>
         <v>14.6</v>
       </c>
-      <c r="P7" s="9" t="s">
+      <c r="P7" t="s">
         <v>45</v>
       </c>
-      <c r="Q7" s="16">
+      <c r="Q7" s="13">
         <f>SUM(N2:N6)</f>
         <v>54.000628750091096</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="9" t="s">
+      <c r="A8" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="12">
         <f>AVERAGE(C2:C7)</f>
         <v>25.078333333333333</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="12">
         <f t="shared" ref="D8:G8" si="2">AVERAGE(D2:D7)</f>
         <v>16.734999999999999</v>
       </c>
-      <c r="E8" s="15">
+      <c r="E8" s="12">
         <f t="shared" si="2"/>
         <v>10.723333333333331</v>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="12">
         <f t="shared" si="2"/>
         <v>26.120000000000005</v>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="12">
         <f t="shared" si="2"/>
         <v>-5.8183333333333325</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="16">
         <v>25</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="16">
         <v>20</v>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="16">
         <v>8</v>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="16">
         <v>30</v>
       </c>
-      <c r="G12" s="19">
+      <c r="G12" s="16">
         <v>-10</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="I13" s="9" t="s">
+      <c r="I13" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="7" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B22" s="13">
+      <c r="B22" s="11">
         <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="13">
+      <c r="B23" s="11">
         <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="13">
+      <c r="B24" s="11">
         <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B25" s="13">
+      <c r="B25" s="11">
         <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="10" t="s">
+      <c r="A26" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B26" s="13">
+      <c r="B26" s="11">
         <v>0.16158637509351526</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="10" t="s">
+      <c r="A27" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B27" s="13">
+      <c r="B27" s="11">
         <v>0.16630487291013885</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B28" s="17">
+      <c r="B28" s="14">
         <f>SUM(B22:B27)</f>
         <v>0.99455791467032073</v>
       </c>

--- a/Courses/Term 3/QAM-III/Case Studies/801 - DATA - S&P500 INDEX.xlsx
+++ b/Courses/Term 3/QAM-III/Case Studies/801 - DATA - S&P500 INDEX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MBA\Courses\Term 3\QAM-III\Case Studies\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B9F5547-157B-4E81-AAE4-43A636636749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50175ED6-2A02-45A6-B6E7-A1861CB81E50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{B2BED8D6-8C7E-0E42-9D17-93C443EBC8CA}"/>
   </bookViews>
